--- a/survey_templates/047_plant_preference_quiz--survey_templates.xlsx
+++ b/survey_templates/047_plant_preference_quiz--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -594,7 +594,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>What age group best describes your target audience?</t>
+          <t>Target Age Group</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -801,7 +801,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>What type of plants do you prefer?</t>
+          <t>Plant Type 2</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>What age group best describes your target audience?</t>
+          <t>Plant Seller Ages 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>houseplant_category_2</t>
+          <t>houseplant_category_2_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Which houseplant category is most important to you?</t>
+          <t>Houseplant Category 2 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1077,7 +1077,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>How sensitive are you about plants?</t>
+          <t>Plant Sensitivities</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1806,7 +1806,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>houseplant_category_2_choices</t>
+          <t>houseplant_category_2_2_choices</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1823,7 +1823,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>houseplant_category_2_choices</t>
+          <t>houseplant_category_2_2_choices</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
